--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="78">
   <si>
     <t/>
   </si>
@@ -218,6 +218,33 @@
   </si>
   <si>
     <t>26</t>
+  </si>
+  <si>
+    <t>20143995</t>
+  </si>
+  <si>
+    <t>HS KRETEK MATCHA 12</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20143913</t>
+  </si>
+  <si>
+    <t>MR.LONG KRTK ULTMT12</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20143993</t>
+  </si>
+  <si>
+    <t>HS APLMNT ORG BOST20</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
 </sst>
 </file>
@@ -610,7 +637,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1080,6 +1107,66 @@
         <v>5</v>
       </c>
     </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="81">
   <si>
     <t/>
   </si>
@@ -245,6 +245,15 @@
   </si>
   <si>
     <t>29</t>
+  </si>
+  <si>
+    <t>20143912</t>
+  </si>
+  <si>
+    <t>MD KRETEK BLACK 12S</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
 </sst>
 </file>
@@ -637,7 +646,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1167,6 +1176,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/IAP01N.xlsx
+++ b/IAP01N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="82">
   <si>
     <t/>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>25</t>
+  </si>
+  <si>
+    <t>TG</t>
   </si>
   <si>
     <t>20143094</t>
@@ -1093,35 +1096,35 @@
         <v>65</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F23" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -1130,18 +1133,18 @@
         <v>4</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
@@ -1150,7 +1153,7 @@
         <v>4</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>5</v>
@@ -1158,10 +1161,10 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
@@ -1170,18 +1173,18 @@
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
@@ -1190,7 +1193,7 @@
         <v>4</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
